--- a/PartsOrdering/DoombaDigikeyOrder.xlsx
+++ b/PartsOrdering/DoombaDigikeyOrder.xlsx
@@ -5,19 +5,20 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ocanath\OcanathProj\doomba\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ocanath\OcanathProj\doomba\PartsOrdering\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2FAA318-C03D-474A-8907-FD22F9B8B7DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDF8E88D-7A47-4FC0-A109-5C3888712C80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{EE240DF0-CAF0-4CF5-AF43-2CB973B6432D}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{EE240DF0-CAF0-4CF5-AF43-2CB973B6432D}"/>
   </bookViews>
   <sheets>
     <sheet name="All" sheetId="5" r:id="rId1"/>
-    <sheet name="usb-rs485-bottom-pos" sheetId="1" r:id="rId2"/>
-    <sheet name="doomba-bdc-pcb-bottom-pos" sheetId="2" r:id="rId3"/>
-    <sheet name="foc-pcb-bottom-pos" sheetId="3" r:id="rId4"/>
-    <sheet name="robot-cortex-top-pos" sheetId="4" r:id="rId5"/>
+    <sheet name="Sheet1" sheetId="6" r:id="rId2"/>
+    <sheet name="usb-rs485-bottom-pos" sheetId="1" r:id="rId3"/>
+    <sheet name="doomba-bdc-pcb-bottom-pos" sheetId="2" r:id="rId4"/>
+    <sheet name="foc-pcb-bottom-pos" sheetId="3" r:id="rId5"/>
+    <sheet name="robot-cortex-top-pos" sheetId="4" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="513" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="130">
   <si>
     <t>Ref</t>
   </si>
@@ -421,6 +422,18 @@
   </si>
   <si>
     <t>C12</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Quantity</t>
+  </si>
+  <si>
+    <t>4-SMD, No Lead</t>
+  </si>
+  <si>
+    <t>NumBoards</t>
   </si>
 </sst>
 </file>
@@ -792,14 +805,345 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9BA7B6C-8700-48E5-90C0-57035B8D3190}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="34.140625" customWidth="1"/>
+    <col min="2" max="2" width="22.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>103</v>
+      </c>
+      <c r="B4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" t="s">
+        <v>55</v>
+      </c>
+      <c r="C6">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>123</v>
+      </c>
+      <c r="B7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>100</v>
+      </c>
+      <c r="B10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>104</v>
+      </c>
+      <c r="B11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>94</v>
+      </c>
+      <c r="B13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>8</v>
+      </c>
+      <c r="B14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>470</v>
+      </c>
+      <c r="B15" t="s">
+        <v>27</v>
+      </c>
+      <c r="C15">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>102</v>
+      </c>
+      <c r="B16" t="s">
+        <v>27</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>29</v>
+      </c>
+      <c r="B17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>86</v>
+      </c>
+      <c r="B18" t="s">
+        <v>87</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>36</v>
+      </c>
+      <c r="B19" t="s">
+        <v>128</v>
+      </c>
+      <c r="C19">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>83</v>
+      </c>
+      <c r="B20" t="s">
+        <v>83</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>107</v>
+      </c>
+      <c r="B21" t="s">
+        <v>106</v>
+      </c>
+      <c r="C21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>92</v>
+      </c>
+      <c r="B22" t="s">
+        <v>91</v>
+      </c>
+      <c r="C22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>40</v>
+      </c>
+      <c r="B23" t="s">
+        <v>39</v>
+      </c>
+      <c r="C23">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>52</v>
+      </c>
+      <c r="B24" t="s">
+        <v>51</v>
+      </c>
+      <c r="C24">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>45</v>
+      </c>
+      <c r="B25" t="s">
+        <v>45</v>
+      </c>
+      <c r="C25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>43</v>
+      </c>
+      <c r="B26" t="s">
+        <v>42</v>
+      </c>
+      <c r="C26">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>49</v>
+      </c>
+      <c r="B27" t="s">
+        <v>48</v>
+      </c>
+      <c r="C27">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>34</v>
+      </c>
+      <c r="B28" t="s">
+        <v>35</v>
+      </c>
+      <c r="C28">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{622979C4-0C09-4DCC-9B43-463996CCD735}">
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B1">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2431C47-3BED-4806-8E51-BC3E032BE07F}">
   <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1131,7 +1475,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB52C270-F0BB-48A0-BD0A-1C609CFF7F19}">
   <dimension ref="A1:G32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1877,7 +2221,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{541BB1E6-922C-462D-9B02-CD4DE07166E6}">
   <dimension ref="A1:G42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2853,7 +3197,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6824632-FD5B-4BDB-AFC7-AD740F4D9812}">
   <dimension ref="A1:G38"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
